--- a/data/exports/黄老师/dist_order_2026-08-31.xlsx
+++ b/data/exports/黄老师/dist_order_2026-08-31.xlsx
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>前程似锦 </t>
+          <t>前程似锦</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
